--- a/tests/fixtures/purchases/Tbl_PO1_2026-09-25.xlsx
+++ b/tests/fixtures/purchases/Tbl_PO1_2026-09-25.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Q13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -877,9 +877,221 @@
         <v>3600</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10">
+        <v>11091</v>
+      </c>
+      <c r="B10" t="str">
+        <v>FB</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Q-26-011091</v>
+      </c>
+      <c r="D10" s="1" t="d">
+        <v>2026-09-21T00:00:00.000Z</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Rental_Quote</v>
+      </c>
+      <c r="F10" t="str">
+        <v>UNI100</v>
+      </c>
+      <c r="G10" t="str">
+        <v>United Rentals (North America)</v>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v>scissor lifts, quote</v>
+      </c>
+      <c r="L10" s="1" t="d">
+        <v>2026-09-24T00:00:00.000Z</v>
+      </c>
+      <c r="M10" t="str">
+        <v/>
+      </c>
+      <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>11090</v>
+      </c>
+      <c r="B11" t="str">
+        <v>FB</v>
+      </c>
+      <c r="C11" t="str">
+        <v>26-011090</v>
+      </c>
+      <c r="D11" s="1" t="d">
+        <v>2026-09-22T00:00:00.000Z</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Material</v>
+      </c>
+      <c r="F11" t="str">
+        <v>500221</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Uline Shipping Supplies</v>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v>gloves, no job on the PO</v>
+      </c>
+      <c r="L11" s="1" t="d">
+        <v>2026-09-25T00:00:00.000Z</v>
+      </c>
+      <c r="M11" t="str">
+        <v/>
+      </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>11089</v>
+      </c>
+      <c r="B12" t="str">
+        <v>FB</v>
+      </c>
+      <c r="C12" t="str">
+        <v>26.01</v>
+      </c>
+      <c r="D12" s="1" t="d">
+        <v>2026-09-23T00:00:00.000Z</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="F12" t="str">
+        <v>UNI100</v>
+      </c>
+      <c r="G12" t="str">
+        <v>United Rentals (North America)</v>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12" t="str">
+        <v>50-60-225121</v>
+      </c>
+      <c r="K12" t="str">
+        <v>light tower, number shared</v>
+      </c>
+      <c r="L12" s="1" t="d">
+        <v>2026-09-26T00:00:00.000Z</v>
+      </c>
+      <c r="M12" t="str">
+        <v/>
+      </c>
+      <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P12" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q12">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>11088</v>
+      </c>
+      <c r="B13" t="str">
+        <v>FB</v>
+      </c>
+      <c r="C13" t="str">
+        <v>26.01</v>
+      </c>
+      <c r="D13" s="1" t="d">
+        <v>2026-09-24T00:00:00.000Z</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="F13" t="str">
+        <v>UNI100</v>
+      </c>
+      <c r="G13" t="str">
+        <v>United Rentals (North America)</v>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
+      <c r="J13" t="str">
+        <v>50-60-225104</v>
+      </c>
+      <c r="K13" t="str">
+        <v>light tower, number shared too</v>
+      </c>
+      <c r="L13" s="1" t="d">
+        <v>2026-09-27T00:00:00.000Z</v>
+      </c>
+      <c r="M13" t="str">
+        <v/>
+      </c>
+      <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13" t="b">
+        <v>0</v>
+      </c>
+      <c r="P13" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q13">
+        <v>700</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q13"/>
   </ignoredErrors>
 </worksheet>
 </file>